--- a/final/siruk-barcodes.xlsx
+++ b/final/siruk-barcodes.xlsx
@@ -10433,7 +10433,7 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>4610011707933</t>
+          <t>4620202548771</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>4610011707940</t>
+          <t>4620202548788</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>4610011707957</t>
+          <t>4620202548801</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>4610011706646</t>
+          <t>4620202548832</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>4610011706271</t>
+          <t>4620202548849</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
